--- a/data/trans_bre/LAWTONB_2R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Clase-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 32,41</t>
+          <t>1,28; 34,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 14,86</t>
+          <t>-19,17; 12,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 24,57</t>
+          <t>-4,11; 24,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 15,29</t>
+          <t>0,58; 15,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 1290,7</t>
+          <t>-35,48; 1336,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-87,05; 990,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 550,06</t>
+          <t>5,94; 573,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 33,84</t>
+          <t>-10,33; 34,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 37,63</t>
+          <t>-7,88; 34,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 38,34</t>
+          <t>-11,66; 37,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 12,96</t>
+          <t>-4,37; 12,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 609,56</t>
+          <t>-100,0; 692,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,54; 568,28</t>
+          <t>-60,82; 563,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 471,47</t>
+          <t>-87,97; 451,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,38; 161,55</t>
+          <t>-34,97; 167,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 29,03</t>
+          <t>-8,16; 30,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 23,05</t>
+          <t>-5,23; 21,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 25,66</t>
+          <t>-3,78; 27,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 24,23</t>
+          <t>2,79; 23,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 484,89</t>
+          <t>-63,88; 469,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 237,48</t>
+          <t>-29,42; 207,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 332,31</t>
+          <t>-32,2; 335,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,45; 216,24</t>
+          <t>14,33; 211,48</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 11,13</t>
+          <t>-7,46; 10,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 11,47</t>
+          <t>-14,52; 11,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 15,52</t>
+          <t>-4,18; 17,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -1,21</t>
+          <t>-23,53; -1,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 83,25</t>
+          <t>-46,15; 82,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 46,54</t>
+          <t>-48,94; 44,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 134,38</t>
+          <t>-25,84; 138,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,06; -7,13</t>
+          <t>-91,78; -6,74</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 27,2</t>
+          <t>-0,55; 25,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 22,07</t>
+          <t>1,01; 21,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 10,73</t>
+          <t>-7,12; 12,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 19,44</t>
+          <t>3,79; 19,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 424,1</t>
+          <t>-2,35; 517,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 147,29</t>
+          <t>1,03; 142,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 56,35</t>
+          <t>-26,5; 71,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 118,01</t>
+          <t>13,14; 110,67</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 19,3</t>
+          <t>-60,07; 19,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,33; 29,38</t>
+          <t>19,65; 28,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 13,92</t>
+          <t>-66,87; 4,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 67,79</t>
+          <t>-66,85; 15,88</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,08</t>
+          <t>1,29; 10,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 10,51</t>
+          <t>0,25; 10,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 12,87</t>
+          <t>4,51; 13,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 13,21</t>
+          <t>-5,96; 12,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 95,15</t>
+          <t>6,01; 95,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 57,13</t>
+          <t>1,05; 59,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,58; 99,63</t>
+          <t>26,15; 105,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 84,33</t>
+          <t>-31,33; 80,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/LAWTONB_2R3-Clase-trans_bre.xlsx
+++ b/data/trans_bre/LAWTONB_2R3-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>146,94%</t>
+          <t>136,77%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 34,48</t>
+          <t>0,33; 33,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 12,85</t>
+          <t>-18,92; 14,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 24,28</t>
+          <t>-3,72; 25,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 15,15</t>
+          <t>0,36; 15,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 1336,24</t>
+          <t>-22,74; 1640,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-66,61; 1147,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 573,08</t>
+          <t>-2,8; 495,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 34,38</t>
+          <t>-11,09; 36,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 34,11</t>
+          <t>-7,97; 38,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 37,23</t>
+          <t>-11,51; 37,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 12,66</t>
+          <t>-4,51; 13,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 692,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,82; 563,85</t>
+          <t>-62,38; 659,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,97; 451,16</t>
+          <t>-73,02; 451,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 167,35</t>
+          <t>-34,05; 218,4</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,09</t>
+          <t>15,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>118,69%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 30,14</t>
+          <t>-5,48; 28,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 21,77</t>
+          <t>-5,0; 21,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 27,14</t>
+          <t>-4,4; 25,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 23,32</t>
+          <t>5,22; 27,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 469,22</t>
+          <t>-56,3; 460,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 207,35</t>
+          <t>-30,41; 213,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 335,04</t>
+          <t>-37,27; 312,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 211,48</t>
+          <t>23,69; 269,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-15,0</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-68,38%</t>
+          <t>-11,03%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 10,63</t>
+          <t>-8,11; 9,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 11,06</t>
+          <t>-14,76; 11,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 17,01</t>
+          <t>-3,19; 18,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,53; -1,8</t>
+          <t>-8,57; 3,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 82,58</t>
+          <t>-47,68; 84,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,94; 44,4</t>
+          <t>-48,24; 47,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 138,11</t>
+          <t>-21,2; 141,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,78; -6,74</t>
+          <t>-35,54; 20,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,65</t>
+          <t>12,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 25,76</t>
+          <t>0,48; 25,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 21,99</t>
+          <t>0,28; 21,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 12,75</t>
+          <t>-8,94; 10,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 19,27</t>
+          <t>4,09; 20,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 517,96</t>
+          <t>-3,31; 366,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 142,45</t>
+          <t>0,92; 142,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 71,42</t>
+          <t>-30,64; 57,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 110,67</t>
+          <t>14,9; 121,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-32,93</t>
+          <t>-33,12</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-49,2%</t>
+          <t>-49,23%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 19,34</t>
+          <t>-82,39; 18,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 28,95</t>
+          <t>20,08; 29,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,87; 4,59</t>
+          <t>-65,51; 13,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 15,88</t>
+          <t>-65,67; 54,35</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>12,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>78,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,02</t>
+          <t>1,42; 10,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 10,46</t>
+          <t>0,65; 10,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,49</t>
+          <t>4,14; 12,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 12,91</t>
+          <t>9,44; 15,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 95,24</t>
+          <t>7,97; 94,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 59,64</t>
+          <t>2,65; 57,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,15; 105,36</t>
+          <t>23,54; 99,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 80,0</t>
+          <t>52,5; 110,68</t>
         </is>
       </c>
     </row>
